--- a/credit_application_forms/035_personal_financial_statement_form--credit_application_forms.xlsx
+++ b/credit_application_forms/035_personal_financial_statement_form--credit_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>investment_property</t>
+          <t>investment property</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>debt_1</t>
+          <t>debt 1</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>debt_2</t>
+          <t>debt 2</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>debt_3</t>
+          <t>debt 3</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>tax_debt</t>
+          <t>tax debt</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>utility_bills</t>
+          <t>utility bills</t>
         </is>
       </c>
     </row>
